--- a/engine_package/Res/MuDataEditor/天使之战_v1.0.0.0/In/cfg_popover.xlsx
+++ b/engine_package/Res/MuDataEditor/天使之战_v1.0.0.0/In/cfg_popover.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="cfg_popover" sheetId="1" r:id="rId1"/>
@@ -2118,7 +2118,7 @@
         <v>0</v>
       </c>
       <c r="F30" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31" customFormat="1" spans="1:6">
